--- a/examples/ornek-brief-battlefield-6.xlsx
+++ b/examples/ornek-brief-battlefield-6.xlsx
@@ -536,7 +536,7 @@
 H2: Battlefield 6 Hikâyesi
 H2: Battlefield 6 Oynanışı ve Oyun Modları
 H3: Çok Oyunculu Modlar ve REDSEC
-H2: Battlefield 6 Atmosferi, Ses Tasarımı ve Müziği
+H2: Battlefield 6 Atmosferi ve Ses Tasarımı
 H2: Battlefield 6'da Öne Çıkan Özellikler
 H2: GeForce NOW ile Battlefield 6 Deneyimi
 H3: Battlefield 6'yı GAME+ ile Oynamak
@@ -558,7 +558,7 @@
 H2 · GeForce NOW'da Nasıl Oynanır: Yalnız erişim yanıtı. Oyun kütüphanede mi, hangi mağaza hesabıyla bağlanıyor, kurulum gerekiyor mu, ücretsiz mod varsa şartı ne. Künye bilgisi girişte verildiği için burada tekrarlanmaz.
 H2 · Hikâyesi: Kurulum (hangi yıl, hangi çatışma, kime karşı), oynanan birlik, bölümlerin geçtiği yerler, anlatı biçimi ve doğrulanmış süre. Olay örgüsü, dönüm noktaları ve son yazılmaz.
 H2 · Oynanışı ve Oyun Modları: Hareket ve silah sistemi, sınıflar (madde listesi), araçlar ve yıkım, harita yapısı, geliştirme bağlamı. Alt başlıkta modlar madde listesiyle ve ücretsiz battle royale modu.
-H2 · Atmosferi, Ses Tasarımı ve Müziği: Ton ve sanat tasarımı somut örnekle, ses tasarımı, besteci ve şarkı seçkisi, kazanılan ödüller ile adaylıklar ayrı ayrı.
+H2 · Atmosferi ve Ses Tasarımı: Ton ve sanat tasarımı somut örnekle, ses tasarımı, besteci ve şarkı seçkisi, kazanılan ödüller ile adaylıklar ayrı ayrı.
 H2 · Öne Çıkan Özellikler: Oyunu ayıran başlıklar 6-8 maddelik listede toplanır; bölüm bir cümlelik girişle açılır.
 H2 · GeForce NOW ile Deneyim: Bulutun somut olarak ne değiştirdiği, gecikme, cihaz çeşitliliği, kontrolcü desteği. Alt başlıklarda paketlerin ne sunduğu ve bağlantı hızı tablosu.
 H2 · Sistem Gereksinimleri ve İndirme: PC gereksinimleri tablosu, ardından bulut karşıtlığı. "Bilgisayarım kaldırır mı" burada karşılanır.

--- a/examples/ornek-brief-battlefield-6.xlsx
+++ b/examples/ornek-brief-battlefield-6.xlsx
@@ -499,7 +499,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="409" customHeight="1">
+    <row r="2" ht="396" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Battlefield 6</t>
@@ -553,8 +553,8 @@
               <color rgb="FF10332F"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">TON: Ürün sayfası. Okuyucu ya oyunu tanıyor ve GeForce NOW üzerinden oynayıp oynayamayacağını merak ediyor, ya da oyunu yeni duymuş ve ne olduğuna bakıyor. Her bölüm önce yanıtı verir, açıklama sonra gelir. Kip cümlenin işine göre seçilir: tanım ve kural geniş zaman, kaynaklı veri "-mektedir/-mıştır", anlatı ve atmosfer şimdiki zaman, okuyucuya yönerge ikinci tekil.
-AÇILIŞ: Gövde başlıksız 1-2 paragraflık girişle açılır; oyunu genel olarak tanıtır, puanlar madde listesiyle verilir, resmi dil desteği tek cümleyle belirtilir. Sayfada H1 bulunduğu için bu girişe başlık konmaz. Tür kelimesi ("FPS oyunları") girişte doğal bir cümlenin içinde geçer ve iç link buraya yerleşir.
+            <t>TON: Ürün sayfası. Okuyucu ya oyunu tanıyor ve GeForce NOW'da oynayıp oynayamayacağını merak ediyor, ya da oyunu yeni duymuş. Her bölüm önce yanıtı verir. Kip işe göre: tanım geniş zaman, kaynaklı veri "-mektedir/-mıştır", anlatı şimdiki zaman, yönerge ikinci tekil.
+AÇILIŞ: Başlıksız 1-2 paragraflık giriş (sayfada H1 var); oyunu tanıtır, puanlar madde listesiyle, resmi dil desteği tek cümleyle. Tür kelimesi ("FPS oyunları") girişte doğal bir cümlenin içinde geçer, iç link buraya.
 H2 · GeForce NOW'da Nasıl Oynanır: Yalnız erişim yanıtı. Oyun kütüphanede mi, hangi mağaza hesabıyla bağlanıyor, kurulum gerekiyor mu, ücretsiz mod varsa şartı ne. Künye bilgisi girişte verildiği için burada tekrarlanmaz.
 H2 · Hikâyesi: Kurulum (hangi yıl, hangi çatışma, kime karşı), oynanan birlik, bölümlerin geçtiği yerler, anlatı biçimi ve doğrulanmış süre. Olay örgüsü, dönüm noktaları ve son yazılmaz.
 H2 · Oynanışı ve Oyun Modları: Hareket ve silah sistemi, sınıflar (madde listesi), araçlar ve yıkım, harita yapısı, geliştirme bağlamı. Alt başlıkta modlar madde listesiyle ve ücretsiz battle royale modu.
@@ -564,9 +564,9 @@
 H2 · Sistem Gereksinimleri ve İndirme: PC gereksinimleri tablosu, ardından bulut karşıtlığı. "Bilgisayarım kaldırır mı" burada karşılanır.
 H2 · Ücretsiz mi, Nasıl Başlanır: Erişim modeli, katalogda desteklenen mağazalar ve 3 maddelik numaralı başlama adımları. Bölümün sonunda kısa bir kapanış çağrısı yer alır.
 SSS: Sayfanın ayrı modülünde yer alır ve gövde kelime sayısına dahil değildir.
-BİÇİM: Sınıflar, modlar, puanlar ve öne çıkan özellikler madde listesiyle; bağlantı hızı ve sistem gereksinimleri tabloyla verilir. Önemli terim ve değerler kalın yazılır. İç linkler zaten var olan bir cümlenin içine yerleşir; "şu listeye göz atabilirsin" biçiminde ek cümle kurulmaz.
+BİÇİM: Sınıflar, modlar, puanlar ve öne çıkan özellikler madde listesiyle; bağlantı hızı ve sistem gereksinimleri tabloyla. Önemli terimler kalın. İç link var olan bir cümlenin içine yerleşir, link için ek cümle kurulmaz. Kapanışta bir iki cümleyle oyunu oynamak için Performance ya da Ultimate paketlerinden birinin seçilebileceği söylenip satın almaya çağrılır; fiyat ve paket özelliği yazılmaz.
 UZUNLUK: Ortalama 1200-1500 kelime gövde. Paragraflar en fazla 3-4 cümledir; teknik değerler (GB, Mbps, çözünürlük, süre) rakamla yazılır.
-DİKKAT: Fiyat, indirim ve kampanya bilgisi yazılmaz. Oyunun hangi GAME+ paketiyle oynanabileceği yazılmaz. GFN optimizasyon durumu yazılmaz. Puan, gereksinim, boyut ve dil listesi PC sürümünden alınır. Mağaza listesi katalogdaki variants alanından gelir; oyun başka mağazada satılsa da GFN desteklemiyorsa yazılmaz. Main KW hacminin büyük bölümü çıkış dönemine aittir (Ekim 2025: 135.000, Kasım 2025: 110.000); Mayıs-Temmuz 2026 ortalaması 15.900'dür. </t>
+DİKKAT: Fiyat, indirim ve kampanya bilgisi, oyuna özel paket gerekliliği ve GFN optimizasyon durumu yazılmaz. Puan, gereksinim, boyut ve dil listesi PC sürümünden alınır. Mağaza listesi katalogdaki variants alanından gelir; oyun başka mağazada satılsa da GFN desteklemiyorsa yazılmaz. Main KW hacminin büyük bölümü çıkış dönemine aittir (Ekim 2025: 135.000, Kasım 2025: 110.000); Mayıs-Temmuz 2026 ortalaması 15.900'dür.</t>
           </r>
           <r>
             <rPr>

--- a/examples/ornek-brief-battlefield-6.xlsx
+++ b/examples/ornek-brief-battlefield-6.xlsx
@@ -564,7 +564,7 @@
 H2 · Sistem Gereksinimleri ve İndirme: PC gereksinimleri tablosu, ardından bulut karşıtlığı. "Bilgisayarım kaldırır mı" burada karşılanır.
 H2 · Ücretsiz mi, Nasıl Başlanır: Erişim modeli, katalogda desteklenen mağazalar ve 3 maddelik numaralı başlama adımları. Bölümün sonunda kısa bir kapanış çağrısı yer alır.
 SSS: Sayfanın ayrı modülünde yer alır ve gövde kelime sayısına dahil değildir.
-BİÇİM: Sınıflar, modlar, puanlar ve öne çıkan özellikler madde listesiyle; bağlantı hızı ve sistem gereksinimleri tabloyla. Önemli terimler kalın. İç link var olan bir cümlenin içine yerleşir, link için ek cümle kurulmaz. Kapanışta bir iki cümleyle oyunu oynamak için Performance ya da Ultimate paketlerinden birinin seçilebileceği söylenip satın almaya çağrılır; fiyat ve paket özelliği yazılmaz.
+BİÇİM: Sınıflar, modlar, puanlar ve öne çıkan özellikler madde listesiyle; bağlantı hızı ve sistem gereksinimleri tabloyla. Önemli terimler kalın. İç link var olan bir cümlenin içine yerleşir, link için ek cümle kurulmaz. Kapanışta bir iki cümleyle oyunu oynamak için GeForce NOW Ultimate ya da Performance paketlerinden birinin seçilebileceği söylenip satın almaya çağrılır; fiyat ve paket özelliği yazılmaz.
 UZUNLUK: Ortalama 1200-1500 kelime gövde. Paragraflar en fazla 3-4 cümledir; teknik değerler (GB, Mbps, çözünürlük, süre) rakamla yazılır.
 DİKKAT: Fiyat, indirim ve kampanya bilgisi, oyuna özel paket gerekliliği ve GFN optimizasyon durumu yazılmaz. Puan, gereksinim, boyut ve dil listesi PC sürümünden alınır. Mağaza listesi katalogdaki variants alanından gelir; oyun başka mağazada satılsa da GFN desteklemiyorsa yazılmaz. Main KW hacminin büyük bölümü çıkış dönemine aittir (Ekim 2025: 135.000, Kasım 2025: 110.000); Mayıs-Temmuz 2026 ortalaması 15.900'dür.</t>
           </r>

--- a/examples/ornek-brief-battlefield-6.xlsx
+++ b/examples/ornek-brief-battlefield-6.xlsx
@@ -604,11 +604,11 @@
 3. Battlefield 6 kaç GB?
    Yanıtta: PC kurulum boyutu ve bulut üzerinden oynarken indirme gerekmediği.
 4. Battlefield 6 Türkçe mi?
-   Yanıtta: resmi arayüz ve altyazı desteği durumu.
+   Yanıtta: resmi Türkçe dil desteği olmadığı (arayüz, altyazı ve seslendirme); desteklenen dillerden örnek.
 5. Bilgisayarım Battlefield 6'yı kaldırır mı?
    Yanıtta: PC gereksinimi ile bulut üzerinden oynama arasındaki fark.
 6. Battlefield 6'da hikâye modu var mı, kaç saat sürüyor?
-   Yanıtta: kampanyanın varlığı ve yaklaşık süresi.
+   Yanıtta: hikâye modunun varlığı ve yaklaşık süresi.
 7. Battlefield 6 RedSec nedir, battle royale ücretsiz mi?
    Yanıtta: RedSec'in Battlefield 6 ile ilişkisi ve erişim koşulu.
 8. Battlefield 6 çevrimdışı oynanabilir mi?

--- a/examples/ornek-brief-battlefield-6.xlsx
+++ b/examples/ornek-brief-battlefield-6.xlsx
@@ -499,7 +499,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="396" customHeight="1">
+    <row r="2" ht="383" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Battlefield 6</t>
@@ -532,13 +532,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>H2: Battlefield 6 GeForce NOW'da Nasıl Oynanır?
-H2: Battlefield 6 Hikâyesi
+          <t>H2: Battlefield 6 Hikâyesi
 H2: Battlefield 6 Oynanışı ve Oyun Modları
 H3: Çok Oyunculu Modlar ve REDSEC
 H2: Battlefield 6 Atmosferi ve Ses Tasarımı
 H2: Battlefield 6'da Öne Çıkan Özellikler
-H2: GeForce NOW ile Battlefield 6 Deneyimi
+H2: Battlefield 6 GeForce NOW'da Nasıl Oynanır?
 H3: Battlefield 6'yı GAME+ ile Oynamak
 H3: Bağlantı Hızı ve Görüntü Kalitesi
 H2: Battlefield 6 Sistem Gereksinimleri ve İndirme
@@ -555,12 +554,11 @@
             </rPr>
             <t>TON: Ürün sayfası. Okuyucu ya oyunu tanıyor ve GeForce NOW'da oynayıp oynayamayacağını merak ediyor, ya da oyunu yeni duymuş. Her bölüm önce yanıtı verir. Kip işe göre: tanım geniş zaman, kaynaklı veri "-mektedir/-mıştır", anlatı şimdiki zaman, yönerge ikinci tekil.
 AÇILIŞ: Başlıksız 1-2 paragraflık giriş (sayfada H1 var); oyunu tanıtır, puanlar madde listesiyle, resmi dil desteği tek cümleyle. Tür kelimesi ("FPS oyunları") girişte doğal bir cümlenin içinde geçer, iç link buraya.
-H2 · GeForce NOW'da Nasıl Oynanır: Yalnız erişim yanıtı. Oyun kütüphanede mi, hangi mağaza hesabıyla bağlanıyor, kurulum gerekiyor mu, ücretsiz mod varsa şartı ne. Künye bilgisi girişte verildiği için burada tekrarlanmaz.
 H2 · Hikâyesi: Kurulum (hangi yıl, hangi çatışma, kime karşı), oynanan birlik, bölümlerin geçtiği yerler, anlatı biçimi ve doğrulanmış süre. Olay örgüsü, dönüm noktaları ve son yazılmaz.
 H2 · Oynanışı ve Oyun Modları: Hareket ve silah sistemi, sınıflar (madde listesi), araçlar ve yıkım, harita yapısı, geliştirme bağlamı. Alt başlıkta modlar madde listesiyle ve ücretsiz battle royale modu.
 H2 · Atmosferi ve Ses Tasarımı: Ton ve sanat tasarımı somut örnekle, ses tasarımı, besteci ve şarkı seçkisi, kazanılan ödüller ile adaylıklar ayrı ayrı.
 H2 · Öne Çıkan Özellikler: Oyunu ayıran başlıklar 6-8 maddelik listede toplanır; bölüm bir cümlelik girişle açılır.
-H2 · GeForce NOW ile Deneyim: Bulutun somut olarak ne değiştirdiği, gecikme, cihaz çeşitliliği, kontrolcü desteği. Alt başlıklarda paketlerin ne sunduğu ve bağlantı hızı tablosu.
+H2 · Battlefield 6 GeForce NOW'da Nasıl Oynanır: Erişim yanıtı ve bulut aynı bölümde: oyun kütüphanededir, Steam ya da EA App hesabıyla açılır, kurulum beklenmez, REDSEC için oyuna sahip olmak gerekmez; ardından bulutun ne değiştirdiği, cihaz çeşitliliği ve kumanda desteği. Alt başlıklarda paketlerin sunduğu değerler ve bağlantı hızı tablosu; hız tablosunun altında oyunun HDR ve NVIDIA Reflex desteği. Bölüm, GAME+ H3'ünün hemen öncesinde durur.
 H2 · Sistem Gereksinimleri ve İndirme: PC gereksinimleri tablosu, ardından bulut karşıtlığı. "Bilgisayarım kaldırır mı" burada karşılanır.
 H2 · Ücretsiz mi, Nasıl Başlanır: Erişim modeli, katalogda desteklenen mağazalar ve 3 maddelik numaralı başlama adımları. Bölümün sonunda kısa bir kapanış çağrısı yer alır.
 SSS: Sayfanın ayrı modülünde yer alır ve gövde kelime sayısına dahil değildir.

--- a/examples/ornek-brief-battlefield-6.xlsx
+++ b/examples/ornek-brief-battlefield-6.xlsx
@@ -552,7 +552,7 @@
               <color rgb="FF10332F"/>
               <sz val="10"/>
             </rPr>
-            <t>TON: Ürün sayfası. Okuyucu ya oyunu tanıyor ve GeForce NOW'da oynayıp oynayamayacağını merak ediyor, ya da oyunu yeni duymuş. Her bölüm önce yanıtı verir. Kip işe göre: tanım geniş zaman, kaynaklı veri "-mektedir/-mıştır", anlatı şimdiki zaman, yönerge ikinci tekil.
+            <t>TON: Ürün sayfası. Okuyucu ya oyunu tanıyor ve GeForce NOW'da oynayıp oynayamayacağını merak ediyor, ya da oyunu yeni duymuş. Her bölüm önce yanıtı verir. Kip işe göre: tanım geniş zaman, kaynaklı veri "-mektedir/-mıştır", anlatı şimdiki zaman, hitap her yerde sen.
 AÇILIŞ: Başlıksız 1-2 paragraflık giriş (sayfada H1 var); oyunu tanıtır, puanlar madde listesiyle, resmi dil desteği tek cümleyle. Tür kelimesi ("FPS oyunları") girişte doğal bir cümlenin içinde geçer, iç link buraya.
 H2 · Hikâyesi: Kurulum (hangi yıl, hangi çatışma, kime karşı), oynanan birlik, bölümlerin geçtiği yerler, anlatı biçimi ve doğrulanmış süre. Olay örgüsü, dönüm noktaları ve son yazılmaz.
 H2 · Oynanışı ve Oyun Modları: Hareket ve silah sistemi, sınıflar (madde listesi), araçlar ve yıkım, harita yapısı, geliştirme bağlamı. Alt başlıkta modlar madde listesiyle ve ücretsiz battle royale modu.

--- a/examples/ornek-brief-battlefield-6.xlsx
+++ b/examples/ornek-brief-battlefield-6.xlsx
@@ -532,13 +532,13 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>H2: Battlefield 6 Hikâyesi
+          <t>H2: Battlefield 6 GeForce NOW'da Nasıl Oynanır?
+H2: Battlefield 6 Hikâyesi
 H2: Battlefield 6 Oynanışı ve Oyun Modları
 H3: Çok Oyunculu Modlar ve REDSEC
 H2: Battlefield 6 Atmosferi ve Ses Tasarımı
 H2: Battlefield 6'da Öne Çıkan Özellikler
-H2: Battlefield 6 GeForce NOW'da Nasıl Oynanır?
-H3: Battlefield 6'yı GAME+ ile Oynamak
+H2: Battlefield 6'yı GAME+ ile Oynamak
 H3: Bağlantı Hızı ve Görüntü Kalitesi
 H2: Battlefield 6 Sistem Gereksinimleri ve İndirme
 H2: Battlefield 6 Ücretsiz mi, Nasıl Başlanır?</t>
@@ -552,19 +552,21 @@
               <color rgb="FF10332F"/>
               <sz val="10"/>
             </rPr>
-            <t>TON: Ürün sayfası. Okuyucu ya oyunu tanıyor ve GeForce NOW'da oynayıp oynayamayacağını merak ediyor, ya da oyunu yeni duymuş. Her bölüm önce yanıtı verir. Kip işe göre: tanım geniş zaman, kaynaklı veri "-mektedir/-mıştır", anlatı şimdiki zaman, hitap her yerde sen.
+            <t>TON: Ürün sayfası; önce yanıt, sonra açıklama. Kip işe göre: tanım geniş zaman, veri -mektedir/-mıştır, anlatı şimdiki zaman, hitap her yerde sen.
 AÇILIŞ: Başlıksız 1-2 paragraflık giriş (sayfada H1 var); oyunu tanıtır, puanlar madde listesiyle, resmi dil desteği tek cümleyle. Tür kelimesi ("FPS oyunları") girişte doğal bir cümlenin içinde geçer, iç link buraya.
+H2 · Battlefield 6 GeForce NOW'da Nasıl Oynanır: İlk H2. Erişim yanıtı ve bulutun kazandırdıkları: oyun kütüphanededir, Steam ya da EA App hesabıyla açılır, kurulum beklenmez, REDSEC için oyuna sahip olmak gerekmez; oyunun NVIDIA sunucularında çalıştığı, cihaz çeşitliliği ve kumanda desteği.
 H2 · Hikâyesi: Kurulum (hangi yıl, hangi çatışma, kime karşı), oynanan birlik, bölümlerin geçtiği yerler, anlatı biçimi ve doğrulanmış süre. Olay örgüsü, dönüm noktaları ve son yazılmaz.
 H2 · Oynanışı ve Oyun Modları: Hareket ve silah sistemi, sınıflar (madde listesi), araçlar ve yıkım, harita yapısı, geliştirme bağlamı. Alt başlıkta modlar madde listesiyle ve ücretsiz battle royale modu.
 H2 · Atmosferi ve Ses Tasarımı: Ton ve sanat tasarımı somut örnekle, ses tasarımı, besteci ve şarkı seçkisi, kazanılan ödüller ile adaylıklar ayrı ayrı.
 H2 · Öne Çıkan Özellikler: Oyunu ayıran başlıklar 6-8 maddelik listede toplanır; bölüm bir cümlelik girişle açılır.
-H2 · Battlefield 6 GeForce NOW'da Nasıl Oynanır: Erişim yanıtı ve bulut aynı bölümde: oyun kütüphanededir, Steam ya da EA App hesabıyla açılır, kurulum beklenmez, REDSEC için oyuna sahip olmak gerekmez; ardından bulutun ne değiştirdiği, cihaz çeşitliliği ve kumanda desteği. Alt başlıklarda paketlerin sunduğu değerler ve bağlantı hızı tablosu; hız tablosunun altında oyunun HDR ve NVIDIA Reflex desteği. Bölüm, GAME+ H3'ünün hemen öncesinde durur.
+H2 · GAME+ ile Oynamak: Steam ya da EA App hesabıyla açıldığı, satın almış olmanın yeterli olduğu; paketlerin sunduğu değerler anlatılır, gereken paket yazılmaz.
+H3 · Bağlantı Hızı ve Görüntü Kalitesi: GAME+ Türkiye / NVIDIA global hız tablosu (720p/60 15, 1080p/60 25, 4K/120 45 Mbps) ve gecikme notu (80 ms altı, ideal 40 ms); oyunun HDR ve NVIDIA Reflex desteği yazılır.
 H2 · Sistem Gereksinimleri ve İndirme: PC gereksinimleri tablosu, ardından bulut karşıtlığı. "Bilgisayarım kaldırır mı" burada karşılanır.
 H2 · Ücretsiz mi, Nasıl Başlanır: Erişim modeli, katalogda desteklenen mağazalar ve 3 maddelik numaralı başlama adımları. Bölümün sonunda kısa bir kapanış çağrısı yer alır.
 SSS: Sayfanın ayrı modülünde yer alır ve gövde kelime sayısına dahil değildir.
-BİÇİM: Sınıflar, modlar, puanlar ve öne çıkan özellikler madde listesiyle; bağlantı hızı ve sistem gereksinimleri tabloyla. Önemli terimler kalın. İç link var olan bir cümlenin içine yerleşir, link için ek cümle kurulmaz. Kapanışta bir iki cümleyle oyunu oynamak için GeForce NOW Ultimate ya da Performance paketlerinden birinin seçilebileceği söylenip satın almaya çağrılır; fiyat ve paket özelliği yazılmaz.
-UZUNLUK: Ortalama 1200-1500 kelime gövde. Paragraflar en fazla 3-4 cümledir; teknik değerler (GB, Mbps, çözünürlük, süre) rakamla yazılır.
-DİKKAT: Fiyat, indirim ve kampanya bilgisi, oyuna özel paket gerekliliği ve GFN optimizasyon durumu yazılmaz. Puan, gereksinim, boyut ve dil listesi PC sürümünden alınır. Mağaza listesi katalogdaki variants alanından gelir; oyun başka mağazada satılsa da GFN desteklemiyorsa yazılmaz. Main KW hacminin büyük bölümü çıkış dönemine aittir (Ekim 2025: 135.000, Kasım 2025: 110.000); Mayıs-Temmuz 2026 ortalaması 15.900'dür.</t>
+BİÇİM: Sınıflar, modlar, puanlar ve öne çıkan özellikler madde listesiyle; hız ve gereksinim tablosu; önemli terimler kalın; link cümle içinde. Oyun bölümlerinde 2-4 yerde oynanış GeForce NOW'a bağlanır. Kapanışta GeForce NOW Ultimate ya da Performance önerisi; fiyat ve paket özelliği yazılmaz.
+UZUNLUK: Ort. 1200-1500 kelime; paragraf en fazla 3-4 cümle, teknik değerler rakamla.
+DİKKAT: Fiyat, kampanya, gereken GAME+ paketi ve GFN optimizasyonu yazılmaz; değerler PC sürümünden alınır. Mağazalar katalogdaki variants alanından gelir (Epic yazılmaz). Hacmin çoğu çıkış dönemine ait (Eki 2025: 135.000, Kas 2025: 110.000); May-Tem 2026 ort. 15.900.</t>
           </r>
           <r>
             <rPr>
@@ -584,9 +586,9 @@
 2. en iyi battle royale oyunları : https://gameplus.com.tr/blog/en-iyi-battle-royale-oyunlari-son-kalan-olmaya-hazir-misin
    H3 · Çok Oyunculu Modlar ve REDSEC bölümünde, REDSEC'in türde nerede durduğu anlatılırken.
 3. cloud gaming nedir : https://gameplus.com.tr/blog/cloud-gaming-nedir
-   H2 · GeForce NOW ile Deneyim bölümünün ilk paragrafında.
+   H2 · GeForce NOW'da Nasıl Oynanır bölümünün ilk paragrafında.
 4. geforce now paketleri : https://gameplus.com.tr/gfn/paketler
-   H3 · GAME+ ile Oynamak bölümünde, paketlerin anlatıldığı cümlede.
+   H2 · GAME+ ile Oynamak bölümünde, paketlerin anlatıldığı cümlede.
 5. battlefield 6 sistem gereksinimleri : https://gameplus.com.tr/blog/battlefield-6-incelemesi-fiyat-sistem-gereksinimleri-ilk-yorumlar
    H2 · Sistem Gereksinimleri ve İndirme bölümünde, tablonun altındaki cümlede.
 6. ücretsiz oyunlar : https://gameplus.com.tr/gfn/oyunlar/oynamasi-ucretsiz

--- a/examples/ornek-brief-battlefield-6.xlsx
+++ b/examples/ornek-brief-battlefield-6.xlsx
@@ -560,7 +560,7 @@
 H2 · Atmosferi ve Ses Tasarımı: Ton ve sanat tasarımı somut örnekle, ses tasarımı, besteci ve şarkı seçkisi, kazanılan ödüller ile adaylıklar ayrı ayrı.
 H2 · Öne Çıkan Özellikler: Oyunu ayıran başlıklar 6-8 maddelik listede toplanır; bölüm bir cümlelik girişle açılır.
 H2 · GAME+ ile Oynamak: Steam ya da EA App hesabıyla açıldığı, satın almış olmanın yeterli olduğu; paketlerin sunduğu değerler anlatılır, gereken paket yazılmaz.
-H3 · Bağlantı Hızı ve Görüntü Kalitesi: GAME+ Türkiye / NVIDIA global hız tablosu (720p/60 15, 1080p/60 25, 4K/120 45 Mbps) ve gecikme notu (80 ms altı, ideal 40 ms); oyunun HDR ve NVIDIA Reflex desteği yazılır.
+H3 · Bağlantı Hızı ve Görüntü Kalitesi: Önerilen bağlantı hızı tablosu (yayın kalitesi / hız / platform; 720p/60 15, 1080p/60 25, 4K/120 45 Mbps+) ve gecikme notu (80 ms altı, ideal 40 ms); oyunun HDR ve NVIDIA Reflex desteği yazılır.
 H2 · Sistem Gereksinimleri ve İndirme: PC gereksinimleri tablosu, ardından bulut karşıtlığı. "Bilgisayarım kaldırır mı" burada karşılanır.
 H2 · Ücretsiz mi, Nasıl Başlanır: Erişim modeli, katalogda desteklenen mağazalar ve 3 maddelik numaralı başlama adımları. Bölümün sonunda kısa bir kapanış çağrısı yer alır.
 SSS: Sayfanın ayrı modülünde yer alır ve gövde kelime sayısına dahil değildir.

--- a/examples/ornek-brief-battlefield-6.xlsx
+++ b/examples/ornek-brief-battlefield-6.xlsx
@@ -538,7 +538,7 @@
 H3: Çok Oyunculu Modlar ve REDSEC
 H2: Battlefield 6 Atmosferi ve Ses Tasarımı
 H2: Battlefield 6'da Öne Çıkan Özellikler
-H2: Battlefield 6'yı GAME+ ile Oynamak
+H2: Battlefield 6'yı GAME+ GeForce NOW ile Oynamak
 H3: Bağlantı Hızı ve Görüntü Kalitesi
 H2: Battlefield 6 Sistem Gereksinimleri ve İndirme
 H2: Battlefield 6 Ücretsiz mi, Nasıl Başlanır?</t>
@@ -559,7 +559,7 @@
 H2 · Oynanışı ve Oyun Modları: Hareket ve silah sistemi, sınıflar (madde listesi), araçlar ve yıkım, harita yapısı, geliştirme bağlamı. Alt başlıkta modlar madde listesiyle ve ücretsiz battle royale modu.
 H2 · Atmosferi ve Ses Tasarımı: Ton ve sanat tasarımı somut örnekle, ses tasarımı, besteci ve şarkı seçkisi, kazanılan ödüller ile adaylıklar ayrı ayrı.
 H2 · Öne Çıkan Özellikler: Oyunu ayıran başlıklar 6-8 maddelik listede toplanır; bölüm bir cümlelik girişle açılır.
-H2 · GAME+ ile Oynamak: Steam ya da EA App hesabıyla açıldığı, satın almış olmanın yeterli olduğu; paketlerin sunduğu değerler anlatılır, gereken paket yazılmaz.
+H2 · GAME+ GeForce NOW ile Oynamak: Steam ya da EA App hesabıyla açıldığı, satın almış olmanın yeterli olduğu; paketlerin sunduğu değerler anlatılır, gereken paket yazılmaz.
 H3 · Bağlantı Hızı ve Görüntü Kalitesi: Önerilen bağlantı hızı tablosu (yayın kalitesi / hız / platform; 720p/60 15, 1080p/60 25, 4K/120 45 Mbps+) ve gecikme notu (80 ms altı, ideal 40 ms); oyunun HDR ve NVIDIA Reflex desteği yazılır.
 H2 · Sistem Gereksinimleri ve İndirme: PC gereksinimleri tablosu, ardından bulut karşıtlığı. "Bilgisayarım kaldırır mı" burada karşılanır.
 H2 · Ücretsiz mi, Nasıl Başlanır: Erişim modeli, katalogda desteklenen mağazalar ve 3 maddelik numaralı başlama adımları. Bölümün sonunda kısa bir kapanış çağrısı yer alır.
@@ -588,7 +588,7 @@
 3. cloud gaming nedir : https://gameplus.com.tr/blog/cloud-gaming-nedir
    H2 · GeForce NOW'da Nasıl Oynanır bölümünün ilk paragrafında.
 4. geforce now paketleri : https://gameplus.com.tr/gfn/paketler
-   H2 · GAME+ ile Oynamak bölümünde, paketlerin anlatıldığı cümlede.
+   H2 · GAME+ GeForce NOW ile Oynamak bölümünde, paketlerin anlatıldığı cümlede.
 5. battlefield 6 sistem gereksinimleri : https://gameplus.com.tr/blog/battlefield-6-incelemesi-fiyat-sistem-gereksinimleri-ilk-yorumlar
    H2 · Sistem Gereksinimleri ve İndirme bölümünde, tablonun altındaki cümlede.
 6. ücretsiz oyunlar : https://gameplus.com.tr/gfn/oyunlar/oynamasi-ucretsiz

--- a/examples/ornek-brief-battlefield-6.xlsx
+++ b/examples/ornek-brief-battlefield-6.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -450,6 +450,7 @@
     <col width="72" customWidth="1" min="7" max="7"/>
     <col width="66" customWidth="1" min="8" max="8"/>
     <col width="58" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -496,6 +497,11 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Yanıt Biçimi</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Resmi Dil Desteği (GeForce NOW)</t>
         </is>
       </c>
     </row>
@@ -628,6 +634,14 @@
 • Doğrulanamayan bilgi yazılmaz; yanıtlanamayan soru listeden çıkarılır.</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Türkçe: Yok
+Arayüz (13): İngilizce, Fransızca, Almanca, İspanyolca, İspanyolca (Latin Amerika), Çince (Basitleştirilmiş), Çince (Geleneksel), Japonca, İtalyanca, Portekizce (Brezilya), Korece, Lehçe, Arapça
+Altyazı (13): İngilizce, Fransızca, Almanca, İspanyolca, İspanyolca (Latin Amerika), Çince (Basitleştirilmiş), Çince (Geleneksel), Japonca, İtalyanca, Portekizce (Brezilya), Korece, Lehçe, Arapça
+Seslendirme (1): İngilizce · Steam sürümünde +10 dil</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/examples/ornek-brief-battlefield-6.xlsx
+++ b/examples/ornek-brief-battlefield-6.xlsx
@@ -581,7 +581,7 @@
               <color rgb="FF10332F"/>
               <sz val="10"/>
             </rPr>
-            <t>Türkçe dil desteği doğrulanamazsa ve resmi, modsuz dil desteği yoksa ilgili H2 ve SSS sorusu çıkarılır.</t>
+            <t xml:space="preserve"> Resmi Türkçe desteği yoktur: ayrı H2 açılmaz, SSS'de "Hayır" ile yanıtlanır.</t>
           </r>
         </is>
       </c>
@@ -610,7 +610,7 @@
 3. Battlefield 6 kaç GB?
    Yanıtta: PC kurulum boyutu ve bulut üzerinden oynarken indirme gerekmediği.
 4. Battlefield 6 Türkçe mi?
-   Yanıtta: resmi Türkçe dil desteği olmadığı (arayüz, altyazı ve seslendirme); desteklenen dillerden örnek.
+   Yanıtta: resmi Türkçe menü, altyazı ve dublaj olmadığı; menü dillerinin sayısı.
 5. Bilgisayarım Battlefield 6'yı kaldırır mı?
    Yanıtta: PC gereksinimi ile bulut üzerinden oynama arasındaki fark.
 6. Battlefield 6'da hikâye modu var mı, kaç saat sürüyor?
@@ -637,9 +637,9 @@
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Türkçe: Yok
-Arayüz (13): İngilizce, Fransızca, Almanca, İspanyolca, İspanyolca (Latin Amerika), Çince (Basitleştirilmiş), Çince (Geleneksel), Japonca, İtalyanca, Portekizce (Brezilya), Korece, Lehçe, Arapça
+Menü (13): İngilizce, Fransızca, Almanca, İspanyolca, İspanyolca (Latin Amerika), Çince (Basitleştirilmiş), Çince (Geleneksel), Japonca, İtalyanca, Portekizce (Brezilya), Korece, Lehçe, Arapça
 Altyazı (13): İngilizce, Fransızca, Almanca, İspanyolca, İspanyolca (Latin Amerika), Çince (Basitleştirilmiş), Çince (Geleneksel), Japonca, İtalyanca, Portekizce (Brezilya), Korece, Lehçe, Arapça
-Seslendirme (1): İngilizce · Steam sürümünde +10 dil</t>
+Seslendirme (1): İngilizce · Steam listesinde +10 dil</t>
         </is>
       </c>
     </row>

--- a/examples/ornek-brief-battlefield-6.xlsx
+++ b/examples/ornek-brief-battlefield-6.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Resmi Dil Desteği (GeForce NOW)</t>
+          <t>Resmi Dil Desteği (PC)</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Türkçe: Yok
+          <t>Türkçe: Yok (teyit: Steam dil tablosu)
 Menü (13): İngilizce, Fransızca, Almanca, İspanyolca, İspanyolca (Latin Amerika), Çince (Basitleştirilmiş), Çince (Geleneksel), Japonca, İtalyanca, Portekizce (Brezilya), Korece, Lehçe, Arapça
 Altyazı (13): İngilizce, Fransızca, Almanca, İspanyolca, İspanyolca (Latin Amerika), Çince (Basitleştirilmiş), Çince (Geleneksel), Japonca, İtalyanca, Portekizce (Brezilya), Korece, Lehçe, Arapça
 Seslendirme (1): İngilizce · Steam listesinde +10 dil</t>
